--- a/prep_and_checklists/JMAK  /ORDER_GUIDE_JMAK  _Wednesday, January 14, 2026  _0.xlsx
+++ b/prep_and_checklists/JMAK  /ORDER_GUIDE_JMAK  _Wednesday, January 14, 2026  _0.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/davidcuvin/purveyor_project/prep_and_checklists/JMAK  /"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C64EFD5-4BA6-C545-B98E-11FF71096B26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46D23E93-7BE3-0C45-BB81-8D0D3029C803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="300" yWindow="1160" windowWidth="29940" windowHeight="17600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="order_guide" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="71">
   <si>
     <t xml:space="preserve">Event:JMAK   Date: Wednesday, January 14, 2026   Guests:N/A  </t>
   </si>
@@ -46,24 +59,12 @@
     <t>Qty</t>
   </si>
   <si>
-    <t>dill 1 lb</t>
-  </si>
-  <si>
     <t>baldor speciality foods inc.</t>
   </si>
   <si>
-    <t>D1</t>
-  </si>
-  <si>
-    <t>blue hill smoked salmon</t>
-  </si>
-  <si>
     <t>liepper and sons llc</t>
   </si>
   <si>
-    <t>5851_XC10088817</t>
-  </si>
-  <si>
     <t>everything bagel</t>
   </si>
   <si>
@@ -73,39 +74,21 @@
     <t>35382_XC8112100</t>
   </si>
   <si>
-    <t>tomato beefsteak large 1 lyr 15 lb</t>
-  </si>
-  <si>
-    <t>TO3C</t>
-  </si>
-  <si>
     <t>sesame</t>
   </si>
   <si>
     <t>35382_XC8112101</t>
   </si>
   <si>
-    <t>orange marmalade bonne maman</t>
-  </si>
-  <si>
     <t>dairyland</t>
   </si>
   <si>
-    <t>100028</t>
-  </si>
-  <si>
     <t>plain bagel</t>
   </si>
   <si>
     <t>35382_XC8112102</t>
   </si>
   <si>
-    <t>cream cheese loaf 3 lb philade</t>
-  </si>
-  <si>
-    <t>DACREAM2A</t>
-  </si>
-  <si>
     <t>bell and evans 10 12oz boneless french cut chicken breasts</t>
   </si>
   <si>
@@ -124,12 +107,6 @@
     <t>9510</t>
   </si>
   <si>
-    <t>blackberries 12x6 oz driscoll</t>
-  </si>
-  <si>
-    <t>BE7</t>
-  </si>
-  <si>
     <t>salmon steelhead steelhead</t>
   </si>
   <si>
@@ -142,108 +119,24 @@
     <t>9520</t>
   </si>
   <si>
-    <t>non pareil capers in brine</t>
-  </si>
-  <si>
-    <t>SPO22J</t>
-  </si>
-  <si>
     <t>blueberry scone</t>
   </si>
   <si>
     <t>9909</t>
   </si>
   <si>
-    <t>strawberry jam</t>
-  </si>
-  <si>
-    <t>10459245</t>
-  </si>
-  <si>
-    <t>scallions iceless 48 ct 4x12 ct</t>
-  </si>
-  <si>
-    <t>SC2A</t>
-  </si>
-  <si>
-    <t>cilantro 1 lb</t>
-  </si>
-  <si>
-    <t>CI1</t>
-  </si>
-  <si>
-    <t>oregano leaves 8 oz</t>
-  </si>
-  <si>
-    <t>SPSPICE99L</t>
-  </si>
-  <si>
-    <t>parsley 1 lb</t>
-  </si>
-  <si>
-    <t>PDOS1</t>
-  </si>
-  <si>
-    <t>feta valbreso sheep french</t>
-  </si>
-  <si>
-    <t>BC430253</t>
-  </si>
-  <si>
     <t>quinoa red conventional</t>
   </si>
   <si>
     <t>923567</t>
   </si>
   <si>
-    <t>farro semi pearled bag 11 lb</t>
-  </si>
-  <si>
-    <t>FLOUR1</t>
-  </si>
-  <si>
-    <t>mixed colored baby carrots</t>
-  </si>
-  <si>
-    <t>CAR991D</t>
-  </si>
-  <si>
-    <t>large medjool dates</t>
-  </si>
-  <si>
-    <t>DA4</t>
-  </si>
-  <si>
-    <t>bulgur wheat coarse box 10 lb</t>
-  </si>
-  <si>
-    <t>FLOUR6</t>
-  </si>
-  <si>
-    <t>shallots peeled 5 lb</t>
-  </si>
-  <si>
-    <t>SH3EA</t>
-  </si>
-  <si>
     <t>miso paste white</t>
   </si>
   <si>
     <t>GSR363</t>
   </si>
   <si>
-    <t>tamari gluten free soy sauce</t>
-  </si>
-  <si>
-    <t>JFC21192</t>
-  </si>
-  <si>
-    <t>tofu extra firm 12x12 oz house</t>
-  </si>
-  <si>
-    <t>TOFU1C</t>
-  </si>
-  <si>
     <t>rice jasmine bag 25 lb</t>
   </si>
   <si>
@@ -256,57 +149,12 @@
     <t>BR9</t>
   </si>
   <si>
-    <t>arugula wild baby 4 lb org</t>
-  </si>
-  <si>
-    <t>ZA6A4</t>
-  </si>
-  <si>
     <t>carrot baby tri color peeled 5 lb</t>
   </si>
   <si>
     <t>CAR91C</t>
   </si>
   <si>
-    <t>almonds sliced natural</t>
-  </si>
-  <si>
-    <t>VN160551</t>
-  </si>
-  <si>
-    <t>micro cilantro 8 oz</t>
-  </si>
-  <si>
-    <t>MIC99F</t>
-  </si>
-  <si>
-    <t>almond marcona roasted and salted</t>
-  </si>
-  <si>
-    <t>SPNU1DDD</t>
-  </si>
-  <si>
-    <t>carrot shredded fine 5 lb</t>
-  </si>
-  <si>
-    <t>CAR96E1</t>
-  </si>
-  <si>
-    <t>cabbage red green mix shredded 5 lb</t>
-  </si>
-  <si>
-    <t>CAB8D</t>
-  </si>
-  <si>
-    <t>sweet potatoes fingerling - japanese</t>
-  </si>
-  <si>
-    <t>natoora</t>
-  </si>
-  <si>
-    <t>20543</t>
-  </si>
-  <si>
     <t>avocado ripe 1 lyr 24 ct 1 2 cs</t>
   </si>
   <si>
@@ -325,108 +173,6 @@
     <t>SAUCE5</t>
   </si>
   <si>
-    <t>sumac ground 18 oz diretta</t>
-  </si>
-  <si>
-    <t>SPSPICE7B</t>
-  </si>
-  <si>
-    <t>seed cumin 1 lb</t>
-  </si>
-  <si>
-    <t>SPSPICE6</t>
-  </si>
-  <si>
-    <t>carrot jumbo 25 lb calo org</t>
-  </si>
-  <si>
-    <t>ZCAR0</t>
-  </si>
-  <si>
-    <t>mint 2.2 lb</t>
-  </si>
-  <si>
-    <t>MI2</t>
-  </si>
-  <si>
-    <t>yogurt greek plain 5% 6x1 lb fage</t>
-  </si>
-  <si>
-    <t>DAYOGURT2</t>
-  </si>
-  <si>
-    <t>yogurt plain 6x32 oz arethusa lcl</t>
-  </si>
-  <si>
-    <t>PAYOGURTA</t>
-  </si>
-  <si>
-    <t>chips regular salt 24x2 oz north fork lcl</t>
-  </si>
-  <si>
-    <t>CHIPSNF4</t>
-  </si>
-  <si>
-    <t>salt and vinegar potato chips</t>
-  </si>
-  <si>
-    <t>CHIPSNF7</t>
-  </si>
-  <si>
-    <t>chips barbeque potato</t>
-  </si>
-  <si>
-    <t>CHIPSNF5</t>
-  </si>
-  <si>
-    <t>chips sour cream and onion 24x2 oz n...</t>
-  </si>
-  <si>
-    <t>CHIPSNF6</t>
-  </si>
-  <si>
-    <t>nuts mix competition salted no</t>
-  </si>
-  <si>
-    <t>SPNU4</t>
-  </si>
-  <si>
-    <t>olives green casteventrano in br</t>
-  </si>
-  <si>
-    <t>SPO22CCC</t>
-  </si>
-  <si>
-    <t>olives red cerignola gg size tin 2</t>
-  </si>
-  <si>
-    <t>SPO22BBB</t>
-  </si>
-  <si>
-    <t>olives green picholine in brine 11 lb</t>
-  </si>
-  <si>
-    <t>SPO5</t>
-  </si>
-  <si>
-    <t>popcorn kernels 50 lb bag</t>
-  </si>
-  <si>
-    <t>GP901</t>
-  </si>
-  <si>
-    <t>pistachio raw shelled tin 4 lb</t>
-  </si>
-  <si>
-    <t>SPNU8AAA</t>
-  </si>
-  <si>
-    <t>cherries dried tart 5 lb bazzini</t>
-  </si>
-  <si>
-    <t>SPFR1AE</t>
-  </si>
-  <si>
     <t>yogurt coconut vegan 8x16 oz cocojune org</t>
   </si>
   <si>
@@ -479,12 +225,6 @@
   </si>
   <si>
     <t>CU5BA</t>
-  </si>
-  <si>
-    <t>celery 24 ct</t>
-  </si>
-  <si>
-    <t>CE</t>
   </si>
   <si>
     <t>1 case</t>
@@ -580,7 +320,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -694,11 +434,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -721,9 +498,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -751,6 +525,42 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="16" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="7" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -969,17 +779,17 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Y988"/>
+  <dimension ref="A1:Y986"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="47.33203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="33.1640625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="12.1640625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="15.5" style="2" customWidth="1"/>
     <col min="4" max="4" width="25.33203125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="54" style="2" customWidth="1"/>
+    <col min="5" max="5" width="69.6640625" style="2" customWidth="1"/>
     <col min="6" max="6" width="21.1640625" style="2" customWidth="1"/>
     <col min="7" max="7" width="21.5" style="2" customWidth="1"/>
-    <col min="8" max="8" width="22.83203125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="29.5" style="2" customWidth="1"/>
     <col min="9" max="10" width="18" style="2" customWidth="1"/>
     <col min="11" max="11" width="18.6640625" style="2" customWidth="1"/>
     <col min="12" max="12" width="18.33203125" style="2" customWidth="1"/>
@@ -989,20 +799,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="60.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-      <c r="K1" s="18"/>
-      <c r="L1" s="19"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="18"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
@@ -1018,24 +828,24 @@
       <c r="Y1" s="1"/>
     </row>
     <row r="2" spans="1:25" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="14" t="s">
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="14" t="s">
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="J2" s="15"/>
-      <c r="K2" s="15"/>
-      <c r="L2" s="16"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="15"/>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
@@ -1051,40 +861,40 @@
       <c r="Y2" s="1"/>
     </row>
     <row r="3" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="J3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="K3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="L3" s="9" t="s">
+      <c r="L3" s="8" t="s">
         <v>7</v>
       </c>
       <c r="M3" s="3"/>
@@ -1102,34 +912,38 @@
       <c r="Y3" s="3"/>
     </row>
     <row r="4" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="10" t="s">
+      <c r="A4" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="I4" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="10"/>
-      <c r="E4" s="11" t="s">
+      <c r="J4" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="K4" s="10" t="s">
         <v>12</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="H4" s="11"/>
-      <c r="I4" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="J4" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="K4" s="11" t="s">
-        <v>16</v>
       </c>
       <c r="L4" s="6"/>
       <c r="M4" s="3"/>
@@ -1147,36 +961,38 @@
       <c r="Y4" s="3"/>
     </row>
     <row r="5" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="10" t="s">
+      <c r="A5" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="10"/>
-      <c r="E5" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="G5" s="12" t="s">
-        <v>30</v>
+      <c r="G5" s="9" t="s">
+        <v>25</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="I5" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="J5" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="K5" s="11" t="s">
-        <v>20</v>
+        <v>66</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="K5" s="10" t="s">
+        <v>14</v>
       </c>
       <c r="L5" s="6"/>
       <c r="M5" s="3"/>
@@ -1194,36 +1010,30 @@
       <c r="Y5" s="3"/>
     </row>
     <row r="6" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="H6" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="I6" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="J6" s="11" t="s">
+      <c r="A6" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="K6" s="11" t="s">
-        <v>25</v>
+      <c r="C6" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J6" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="K6" s="10" t="s">
+        <v>17</v>
       </c>
       <c r="L6" s="6"/>
       <c r="M6" s="3"/>
@@ -1241,28 +1051,30 @@
       <c r="Y6" s="3"/>
     </row>
     <row r="7" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" s="10"/>
+      <c r="A7" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>64</v>
+      </c>
       <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
+      <c r="F7" s="9"/>
       <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="J7" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="K7" s="12" t="s">
-        <v>33</v>
+      <c r="H7" s="9"/>
+      <c r="I7" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>23</v>
       </c>
       <c r="L7" s="4"/>
       <c r="M7" s="3"/>
@@ -1280,28 +1092,30 @@
       <c r="Y7" s="3"/>
     </row>
     <row r="8" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" s="10"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="11"/>
+      <c r="A8" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="E8" s="10"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="10"/>
       <c r="H8" s="10"/>
-      <c r="I8" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="J8" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="K8" s="10" t="s">
-        <v>39</v>
+      <c r="I8" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="K8" s="9" t="s">
+        <v>27</v>
       </c>
       <c r="L8" s="5"/>
       <c r="M8" s="3"/>
@@ -1319,28 +1133,30 @@
       <c r="Y8" s="3"/>
     </row>
     <row r="9" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="D9" s="10"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="10" t="s">
+      <c r="A9" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="J9" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="K9" s="10" t="s">
+      <c r="B9" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="9" t="s">
         <v>43</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E9" s="10"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="K9" s="9" t="s">
+        <v>29</v>
       </c>
       <c r="L9" s="7"/>
       <c r="M9" s="3"/>
@@ -1358,28 +1174,30 @@
       <c r="Y9" s="3"/>
     </row>
     <row r="10" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B10" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="10" t="s">
+      <c r="B10" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="D10" s="10"/>
+      <c r="D10" s="9" t="s">
+        <v>69</v>
+      </c>
       <c r="E10" s="11"/>
-      <c r="F10" s="10"/>
+      <c r="F10" s="9"/>
       <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="J10" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="K10" s="11" t="s">
-        <v>16</v>
+      <c r="H10" s="10"/>
+      <c r="I10" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="J10" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="K10" s="10" t="s">
+        <v>12</v>
       </c>
       <c r="L10" s="6"/>
       <c r="M10" s="3"/>
@@ -1397,28 +1215,30 @@
       <c r="Y10" s="3"/>
     </row>
     <row r="11" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="12"/>
+      <c r="A11" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E11" s="11"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="11"/>
       <c r="H11" s="11"/>
-      <c r="I11" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="J11" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="K11" s="11" t="s">
-        <v>20</v>
+      <c r="I11" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="J11" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="K11" s="10" t="s">
+        <v>14</v>
       </c>
       <c r="L11" s="6"/>
       <c r="M11" s="3"/>
@@ -1436,28 +1256,30 @@
       <c r="Y11" s="3"/>
     </row>
     <row r="12" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D12" s="10"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="J12" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="K12" s="11" t="s">
-        <v>25</v>
+      <c r="A12" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J12" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="K12" s="10" t="s">
+        <v>17</v>
       </c>
       <c r="L12" s="6"/>
       <c r="M12" s="3"/>
@@ -1475,28 +1297,30 @@
       <c r="Y12" s="3"/>
     </row>
     <row r="13" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="J13" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="K13" s="12" t="s">
-        <v>43</v>
+      <c r="A13" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E13" s="11"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="J13" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="K13" s="11" t="s">
+        <v>29</v>
       </c>
       <c r="L13" s="4"/>
       <c r="M13" s="3"/>
@@ -1514,23 +1338,25 @@
       <c r="Y13" s="3"/>
     </row>
     <row r="14" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="D14" s="10"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="12"/>
-      <c r="J14" s="12"/>
-      <c r="K14" s="12"/>
+      <c r="A14" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E14" s="11"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="11"/>
+      <c r="K14" s="11"/>
       <c r="L14" s="4"/>
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
@@ -1547,23 +1373,25 @@
       <c r="Y14" s="3"/>
     </row>
     <row r="15" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="D15" s="10"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
+      <c r="C15" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E15" s="11"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="9"/>
       <c r="L15" s="5"/>
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
@@ -1580,23 +1408,25 @@
       <c r="Y15" s="3"/>
     </row>
     <row r="16" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="D16" s="10"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="12"/>
-      <c r="J16" s="12"/>
-      <c r="K16" s="12"/>
+      <c r="A16" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="E16" s="19"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="11"/>
+      <c r="K16" s="11"/>
       <c r="L16" s="4"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
@@ -1613,23 +1443,25 @@
       <c r="Y16" s="3"/>
     </row>
     <row r="17" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="D17" s="10"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="12"/>
-      <c r="J17" s="12"/>
-      <c r="K17" s="12"/>
+      <c r="A17" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="B17" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="D17" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="E17" s="19"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="11"/>
       <c r="L17" s="4"/>
       <c r="M17" s="3"/>
       <c r="N17" s="3"/>
@@ -1646,23 +1478,25 @@
       <c r="Y17" s="3"/>
     </row>
     <row r="18" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="D18" s="10"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="12"/>
-      <c r="J18" s="12"/>
-      <c r="K18" s="12"/>
+      <c r="A18" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="B18" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="D18" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="E18" s="20"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="11"/>
       <c r="L18" s="4"/>
       <c r="M18" s="3"/>
       <c r="N18" s="3"/>
@@ -1679,23 +1513,25 @@
       <c r="Y18" s="3"/>
     </row>
     <row r="19" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="B19" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="12"/>
-      <c r="K19" s="12"/>
+      <c r="A19" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="B19" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="D19" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="E19" s="29"/>
+      <c r="F19" s="21"/>
+      <c r="G19" s="23"/>
+      <c r="H19" s="21"/>
+      <c r="I19" s="23"/>
+      <c r="J19" s="11"/>
+      <c r="K19" s="11"/>
       <c r="L19" s="4"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
@@ -1712,23 +1548,25 @@
       <c r="Y19" s="3"/>
     </row>
     <row r="20" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="B20" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="D20" s="10"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="10"/>
-      <c r="I20" s="12"/>
-      <c r="J20" s="12"/>
-      <c r="K20" s="12"/>
+      <c r="A20" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="B20" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="D20" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="E20" s="30"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="30"/>
+      <c r="H20" s="30"/>
+      <c r="I20" s="30"/>
+      <c r="J20" s="19"/>
+      <c r="K20" s="11"/>
       <c r="L20" s="4"/>
       <c r="M20" s="3"/>
       <c r="N20" s="3"/>
@@ -1745,24 +1583,14 @@
       <c r="Y20" s="3"/>
     </row>
     <row r="21" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="B21" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="D21" s="10"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="10"/>
-      <c r="J21" s="10"/>
-      <c r="K21" s="10"/>
-      <c r="L21" s="5"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="24"/>
+      <c r="H21" s="24"/>
+      <c r="I21" s="25"/>
+      <c r="J21" s="25"/>
+      <c r="K21" s="25"/>
+      <c r="L21" s="26"/>
       <c r="M21" s="3"/>
       <c r="N21" s="3"/>
       <c r="O21" s="3"/>
@@ -1778,24 +1606,14 @@
       <c r="Y21" s="3"/>
     </row>
     <row r="22" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="12"/>
-      <c r="J22" s="12"/>
-      <c r="K22" s="12"/>
-      <c r="L22" s="4"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="24"/>
+      <c r="I22" s="24"/>
+      <c r="J22" s="24"/>
+      <c r="K22" s="24"/>
+      <c r="L22" s="27"/>
       <c r="M22" s="3"/>
       <c r="N22" s="3"/>
       <c r="O22" s="3"/>
@@ -1811,24 +1629,14 @@
       <c r="Y22" s="3"/>
     </row>
     <row r="23" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="B23" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C23" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="10"/>
-      <c r="H23" s="10"/>
-      <c r="I23" s="12"/>
-      <c r="J23" s="12"/>
-      <c r="K23" s="12"/>
-      <c r="L23" s="4"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="24"/>
+      <c r="H23" s="24"/>
+      <c r="I23" s="24"/>
+      <c r="J23" s="24"/>
+      <c r="K23" s="24"/>
+      <c r="L23" s="27"/>
       <c r="M23" s="3"/>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
@@ -1844,24 +1652,14 @@
       <c r="Y23" s="3"/>
     </row>
     <row r="24" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="B24" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="10"/>
-      <c r="H24" s="10"/>
-      <c r="I24" s="10"/>
-      <c r="J24" s="10"/>
-      <c r="K24" s="10"/>
-      <c r="L24" s="5"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="24"/>
+      <c r="G24" s="25"/>
+      <c r="H24" s="24"/>
+      <c r="I24" s="24"/>
+      <c r="J24" s="24"/>
+      <c r="K24" s="24"/>
+      <c r="L24" s="27"/>
       <c r="M24" s="3"/>
       <c r="N24" s="3"/>
       <c r="O24" s="3"/>
@@ -1877,24 +1675,14 @@
       <c r="Y24" s="3"/>
     </row>
     <row r="25" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="B25" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="10"/>
-      <c r="I25" s="10"/>
-      <c r="J25" s="10"/>
-      <c r="K25" s="10"/>
-      <c r="L25" s="5"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="24"/>
+      <c r="G25" s="25"/>
+      <c r="H25" s="25"/>
+      <c r="I25" s="24"/>
+      <c r="J25" s="24"/>
+      <c r="K25" s="24"/>
+      <c r="L25" s="27"/>
       <c r="M25" s="3"/>
       <c r="N25" s="3"/>
       <c r="O25" s="3"/>
@@ -1910,24 +1698,14 @@
       <c r="Y25" s="3"/>
     </row>
     <row r="26" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="B26" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C26" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="10"/>
-      <c r="I26" s="10"/>
-      <c r="J26" s="10"/>
-      <c r="K26" s="10"/>
-      <c r="L26" s="5"/>
+      <c r="E26" s="25"/>
+      <c r="F26" s="24"/>
+      <c r="G26" s="25"/>
+      <c r="H26" s="25"/>
+      <c r="I26" s="24"/>
+      <c r="J26" s="24"/>
+      <c r="K26" s="24"/>
+      <c r="L26" s="27"/>
       <c r="M26" s="3"/>
       <c r="N26" s="3"/>
       <c r="O26" s="3"/>
@@ -1943,24 +1721,14 @@
       <c r="Y26" s="3"/>
     </row>
     <row r="27" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="B27" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C27" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="D27" s="10"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="12"/>
-      <c r="H27" s="10"/>
-      <c r="I27" s="10"/>
-      <c r="J27" s="10"/>
-      <c r="K27" s="10"/>
-      <c r="L27" s="5"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="24"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="25"/>
+      <c r="I27" s="25"/>
+      <c r="J27" s="25"/>
+      <c r="K27" s="25"/>
+      <c r="L27" s="26"/>
       <c r="M27" s="3"/>
       <c r="N27" s="3"/>
       <c r="O27" s="3"/>
@@ -1976,24 +1744,14 @@
       <c r="Y27" s="3"/>
     </row>
     <row r="28" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="B28" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C28" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="D28" s="10"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="10"/>
-      <c r="G28" s="12"/>
-      <c r="H28" s="12"/>
-      <c r="I28" s="10"/>
-      <c r="J28" s="10"/>
-      <c r="K28" s="10"/>
-      <c r="L28" s="5"/>
+      <c r="E28" s="25"/>
+      <c r="F28" s="24"/>
+      <c r="G28" s="25"/>
+      <c r="H28" s="25"/>
+      <c r="I28" s="25"/>
+      <c r="J28" s="25"/>
+      <c r="K28" s="25"/>
+      <c r="L28" s="26"/>
       <c r="M28" s="3"/>
       <c r="N28" s="3"/>
       <c r="O28" s="3"/>
@@ -2009,24 +1767,14 @@
       <c r="Y28" s="3"/>
     </row>
     <row r="29" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="B29" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C29" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="D29" s="10"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="10"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="12"/>
-      <c r="J29" s="12"/>
-      <c r="K29" s="12"/>
-      <c r="L29" s="4"/>
+      <c r="E29" s="25"/>
+      <c r="F29" s="24"/>
+      <c r="G29" s="25"/>
+      <c r="H29" s="25"/>
+      <c r="I29" s="25"/>
+      <c r="J29" s="25"/>
+      <c r="K29" s="25"/>
+      <c r="L29" s="26"/>
       <c r="M29" s="3"/>
       <c r="N29" s="3"/>
       <c r="O29" s="3"/>
@@ -2042,26 +1790,14 @@
       <c r="Y29" s="3"/>
     </row>
     <row r="30" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="B30" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C30" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="D30" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="E30" s="12"/>
-      <c r="F30" s="10"/>
-      <c r="G30" s="12"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="12"/>
-      <c r="J30" s="12"/>
-      <c r="K30" s="12"/>
-      <c r="L30" s="4"/>
+      <c r="E30" s="25"/>
+      <c r="F30" s="24"/>
+      <c r="G30" s="25"/>
+      <c r="H30" s="25"/>
+      <c r="I30" s="25"/>
+      <c r="J30" s="25"/>
+      <c r="K30" s="25"/>
+      <c r="L30" s="26"/>
       <c r="M30" s="3"/>
       <c r="N30" s="3"/>
       <c r="O30" s="3"/>
@@ -2077,24 +1813,14 @@
       <c r="Y30" s="3"/>
     </row>
     <row r="31" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="B31" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C31" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="D31" s="10"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="10"/>
-      <c r="G31" s="12"/>
-      <c r="H31" s="12"/>
-      <c r="I31" s="12"/>
-      <c r="J31" s="12"/>
-      <c r="K31" s="12"/>
-      <c r="L31" s="4"/>
+      <c r="E31" s="25"/>
+      <c r="F31" s="24"/>
+      <c r="G31" s="25"/>
+      <c r="H31" s="25"/>
+      <c r="I31" s="25"/>
+      <c r="J31" s="25"/>
+      <c r="K31" s="25"/>
+      <c r="L31" s="26"/>
       <c r="M31" s="3"/>
       <c r="N31" s="3"/>
       <c r="O31" s="3"/>
@@ -2110,24 +1836,14 @@
       <c r="Y31" s="3"/>
     </row>
     <row r="32" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="B32" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C32" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="D32" s="10"/>
-      <c r="E32" s="12"/>
-      <c r="F32" s="10"/>
-      <c r="G32" s="12"/>
-      <c r="H32" s="12"/>
-      <c r="I32" s="12"/>
-      <c r="J32" s="12"/>
-      <c r="K32" s="12"/>
-      <c r="L32" s="4"/>
+      <c r="E32" s="25"/>
+      <c r="F32" s="24"/>
+      <c r="G32" s="25"/>
+      <c r="H32" s="25"/>
+      <c r="I32" s="25"/>
+      <c r="J32" s="25"/>
+      <c r="K32" s="25"/>
+      <c r="L32" s="26"/>
       <c r="M32" s="3"/>
       <c r="N32" s="3"/>
       <c r="O32" s="3"/>
@@ -2142,27 +1858,15 @@
       <c r="X32" s="3"/>
       <c r="Y32" s="3"/>
     </row>
-    <row r="33" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="B33" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C33" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="D33" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="E33" s="12"/>
-      <c r="F33" s="10"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="12"/>
-      <c r="I33" s="12"/>
-      <c r="J33" s="12"/>
-      <c r="K33" s="12"/>
-      <c r="L33" s="4"/>
+    <row r="33" spans="5:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E33" s="25"/>
+      <c r="F33" s="24"/>
+      <c r="G33" s="25"/>
+      <c r="H33" s="25"/>
+      <c r="I33" s="25"/>
+      <c r="J33" s="25"/>
+      <c r="K33" s="25"/>
+      <c r="L33" s="26"/>
       <c r="M33" s="3"/>
       <c r="N33" s="3"/>
       <c r="O33" s="3"/>
@@ -2177,27 +1881,15 @@
       <c r="X33" s="3"/>
       <c r="Y33" s="3"/>
     </row>
-    <row r="34" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="B34" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C34" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="D34" s="10" t="s">
-        <v>159</v>
-      </c>
-      <c r="E34" s="12"/>
-      <c r="F34" s="10"/>
-      <c r="G34" s="12"/>
-      <c r="H34" s="12"/>
-      <c r="I34" s="12"/>
-      <c r="J34" s="12"/>
-      <c r="K34" s="12"/>
-      <c r="L34" s="4"/>
+    <row r="34" spans="5:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E34" s="25"/>
+      <c r="F34" s="24"/>
+      <c r="G34" s="25"/>
+      <c r="H34" s="25"/>
+      <c r="I34" s="25"/>
+      <c r="J34" s="25"/>
+      <c r="K34" s="25"/>
+      <c r="L34" s="26"/>
       <c r="M34" s="3"/>
       <c r="N34" s="3"/>
       <c r="O34" s="3"/>
@@ -2212,27 +1904,15 @@
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
-    <row r="35" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="B35" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C35" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="D35" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="E35" s="12"/>
-      <c r="F35" s="10"/>
-      <c r="G35" s="12"/>
-      <c r="H35" s="12"/>
-      <c r="I35" s="12"/>
-      <c r="J35" s="12"/>
-      <c r="K35" s="12"/>
-      <c r="L35" s="4"/>
+    <row r="35" spans="5:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E35" s="25"/>
+      <c r="F35" s="24"/>
+      <c r="G35" s="25"/>
+      <c r="H35" s="25"/>
+      <c r="I35" s="25"/>
+      <c r="J35" s="25"/>
+      <c r="K35" s="25"/>
+      <c r="L35" s="26"/>
       <c r="M35" s="3"/>
       <c r="N35" s="3"/>
       <c r="O35" s="3"/>
@@ -2247,25 +1927,15 @@
       <c r="X35" s="3"/>
       <c r="Y35" s="3"/>
     </row>
-    <row r="36" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="B36" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C36" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="D36" s="10"/>
-      <c r="E36" s="12"/>
-      <c r="F36" s="10"/>
-      <c r="G36" s="12"/>
-      <c r="H36" s="12"/>
-      <c r="I36" s="12"/>
-      <c r="J36" s="12"/>
-      <c r="K36" s="12"/>
-      <c r="L36" s="4"/>
+    <row r="36" spans="5:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E36" s="25"/>
+      <c r="F36" s="24"/>
+      <c r="G36" s="25"/>
+      <c r="H36" s="25"/>
+      <c r="I36" s="25"/>
+      <c r="J36" s="25"/>
+      <c r="K36" s="25"/>
+      <c r="L36" s="26"/>
       <c r="M36" s="3"/>
       <c r="N36" s="3"/>
       <c r="O36" s="3"/>
@@ -2280,25 +1950,15 @@
       <c r="X36" s="3"/>
       <c r="Y36" s="3"/>
     </row>
-    <row r="37" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="B37" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C37" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="D37" s="10"/>
-      <c r="E37" s="12"/>
-      <c r="F37" s="10"/>
-      <c r="G37" s="12"/>
-      <c r="H37" s="12"/>
-      <c r="I37" s="12"/>
-      <c r="J37" s="12"/>
-      <c r="K37" s="12"/>
-      <c r="L37" s="4"/>
+    <row r="37" spans="5:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E37" s="24"/>
+      <c r="F37" s="24"/>
+      <c r="G37" s="24"/>
+      <c r="H37" s="25"/>
+      <c r="I37" s="25"/>
+      <c r="J37" s="25"/>
+      <c r="K37" s="25"/>
+      <c r="L37" s="26"/>
       <c r="M37" s="3"/>
       <c r="N37" s="3"/>
       <c r="O37" s="3"/>
@@ -2313,25 +1973,15 @@
       <c r="X37" s="3"/>
       <c r="Y37" s="3"/>
     </row>
-    <row r="38" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="B38" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C38" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="D38" s="10"/>
-      <c r="E38" s="12"/>
-      <c r="F38" s="10"/>
-      <c r="G38" s="12"/>
-      <c r="H38" s="12"/>
-      <c r="I38" s="12"/>
-      <c r="J38" s="12"/>
-      <c r="K38" s="12"/>
-      <c r="L38" s="4"/>
+    <row r="38" spans="5:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E38" s="24"/>
+      <c r="F38" s="24"/>
+      <c r="G38" s="24"/>
+      <c r="H38" s="24"/>
+      <c r="I38" s="25"/>
+      <c r="J38" s="25"/>
+      <c r="K38" s="25"/>
+      <c r="L38" s="26"/>
       <c r="M38" s="3"/>
       <c r="N38" s="3"/>
       <c r="O38" s="3"/>
@@ -2346,25 +1996,15 @@
       <c r="X38" s="3"/>
       <c r="Y38" s="3"/>
     </row>
-    <row r="39" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="B39" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C39" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="D39" s="10"/>
-      <c r="E39" s="12"/>
-      <c r="F39" s="10"/>
-      <c r="G39" s="12"/>
-      <c r="H39" s="12"/>
-      <c r="I39" s="12"/>
-      <c r="J39" s="12"/>
-      <c r="K39" s="12"/>
-      <c r="L39" s="4"/>
+    <row r="39" spans="5:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E39" s="24"/>
+      <c r="F39" s="24"/>
+      <c r="G39" s="24"/>
+      <c r="H39" s="24"/>
+      <c r="I39" s="25"/>
+      <c r="J39" s="25"/>
+      <c r="K39" s="25"/>
+      <c r="L39" s="26"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
@@ -2379,25 +2019,15 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
     </row>
-    <row r="40" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="B40" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C40" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="D40" s="10"/>
-      <c r="E40" s="10"/>
-      <c r="F40" s="10"/>
-      <c r="G40" s="10"/>
-      <c r="H40" s="12"/>
-      <c r="I40" s="12"/>
-      <c r="J40" s="12"/>
-      <c r="K40" s="12"/>
-      <c r="L40" s="4"/>
+    <row r="40" spans="5:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E40" s="24"/>
+      <c r="F40" s="24"/>
+      <c r="G40" s="24"/>
+      <c r="H40" s="24"/>
+      <c r="I40" s="24"/>
+      <c r="J40" s="24"/>
+      <c r="K40" s="24"/>
+      <c r="L40" s="27"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
@@ -2412,25 +2042,15 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
     </row>
-    <row r="41" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="B41" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C41" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D41" s="10"/>
-      <c r="E41" s="10"/>
-      <c r="F41" s="10"/>
-      <c r="G41" s="10"/>
-      <c r="H41" s="10"/>
-      <c r="I41" s="12"/>
-      <c r="J41" s="12"/>
-      <c r="K41" s="12"/>
-      <c r="L41" s="4"/>
+    <row r="41" spans="5:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E41" s="24"/>
+      <c r="F41" s="24"/>
+      <c r="G41" s="24"/>
+      <c r="H41" s="24"/>
+      <c r="I41" s="24"/>
+      <c r="J41" s="24"/>
+      <c r="K41" s="24"/>
+      <c r="L41" s="28"/>
       <c r="M41" s="3"/>
       <c r="N41" s="3"/>
       <c r="O41" s="3"/>
@@ -2445,25 +2065,15 @@
       <c r="X41" s="3"/>
       <c r="Y41" s="3"/>
     </row>
-    <row r="42" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="B42" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C42" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D42" s="10"/>
-      <c r="E42" s="10"/>
-      <c r="F42" s="10"/>
-      <c r="G42" s="10"/>
-      <c r="H42" s="10"/>
-      <c r="I42" s="10"/>
-      <c r="J42" s="10"/>
-      <c r="K42" s="10"/>
-      <c r="L42" s="5"/>
+    <row r="42" spans="5:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E42" s="24"/>
+      <c r="F42" s="24"/>
+      <c r="G42" s="24"/>
+      <c r="H42" s="24"/>
+      <c r="I42" s="24"/>
+      <c r="J42" s="24"/>
+      <c r="K42" s="24"/>
+      <c r="L42" s="28"/>
       <c r="M42" s="3"/>
       <c r="N42" s="3"/>
       <c r="O42" s="3"/>
@@ -2478,25 +2088,15 @@
       <c r="X42" s="3"/>
       <c r="Y42" s="3"/>
     </row>
-    <row r="43" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="B43" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C43" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="D43" s="10"/>
-      <c r="E43" s="10"/>
-      <c r="F43" s="10"/>
-      <c r="G43" s="10"/>
-      <c r="H43" s="10"/>
-      <c r="I43" s="10"/>
-      <c r="J43" s="10"/>
-      <c r="K43" s="10"/>
-      <c r="L43" s="8"/>
+    <row r="43" spans="5:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E43" s="24"/>
+      <c r="F43" s="24"/>
+      <c r="G43" s="24"/>
+      <c r="H43" s="24"/>
+      <c r="I43" s="24"/>
+      <c r="J43" s="24"/>
+      <c r="K43" s="24"/>
+      <c r="L43" s="28"/>
       <c r="M43" s="3"/>
       <c r="N43" s="3"/>
       <c r="O43" s="3"/>
@@ -2511,25 +2111,15 @@
       <c r="X43" s="3"/>
       <c r="Y43" s="3"/>
     </row>
-    <row r="44" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="B44" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="C44" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="D44" s="10"/>
-      <c r="E44" s="10"/>
-      <c r="F44" s="10"/>
-      <c r="G44" s="10"/>
-      <c r="H44" s="10"/>
-      <c r="I44" s="10"/>
-      <c r="J44" s="10"/>
-      <c r="K44" s="10"/>
-      <c r="L44" s="8"/>
+    <row r="44" spans="5:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E44" s="24"/>
+      <c r="F44" s="24"/>
+      <c r="G44" s="24"/>
+      <c r="H44" s="24"/>
+      <c r="I44" s="24"/>
+      <c r="J44" s="24"/>
+      <c r="K44" s="24"/>
+      <c r="L44" s="28"/>
       <c r="M44" s="3"/>
       <c r="N44" s="3"/>
       <c r="O44" s="3"/>
@@ -2544,27 +2134,15 @@
       <c r="X44" s="3"/>
       <c r="Y44" s="3"/>
     </row>
-    <row r="45" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="B45" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C45" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="D45" s="10" t="s">
-        <v>156</v>
-      </c>
-      <c r="E45" s="10"/>
-      <c r="F45" s="10"/>
-      <c r="G45" s="10"/>
-      <c r="H45" s="10"/>
-      <c r="I45" s="10"/>
-      <c r="J45" s="10"/>
-      <c r="K45" s="10"/>
-      <c r="L45" s="8"/>
+    <row r="45" spans="5:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E45" s="24"/>
+      <c r="F45" s="24"/>
+      <c r="G45" s="24"/>
+      <c r="H45" s="24"/>
+      <c r="I45" s="24"/>
+      <c r="J45" s="24"/>
+      <c r="K45" s="24"/>
+      <c r="L45" s="28"/>
       <c r="M45" s="3"/>
       <c r="N45" s="3"/>
       <c r="O45" s="3"/>
@@ -2579,27 +2157,15 @@
       <c r="X45" s="3"/>
       <c r="Y45" s="3"/>
     </row>
-    <row r="46" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="B46" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C46" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="D46" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="E46" s="10"/>
-      <c r="F46" s="10"/>
-      <c r="G46" s="10"/>
-      <c r="H46" s="10"/>
-      <c r="I46" s="10"/>
-      <c r="J46" s="10"/>
-      <c r="K46" s="10"/>
-      <c r="L46" s="8"/>
+    <row r="46" spans="5:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E46" s="24"/>
+      <c r="F46" s="24"/>
+      <c r="G46" s="24"/>
+      <c r="H46" s="24"/>
+      <c r="I46" s="24"/>
+      <c r="J46" s="24"/>
+      <c r="K46" s="24"/>
+      <c r="L46" s="28"/>
       <c r="M46" s="3"/>
       <c r="N46" s="3"/>
       <c r="O46" s="3"/>
@@ -2614,27 +2180,15 @@
       <c r="X46" s="3"/>
       <c r="Y46" s="3"/>
     </row>
-    <row r="47" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="B47" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C47" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="D47" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="E47" s="10"/>
-      <c r="F47" s="10"/>
-      <c r="G47" s="10"/>
-      <c r="H47" s="10"/>
-      <c r="I47" s="10"/>
-      <c r="J47" s="10"/>
-      <c r="K47" s="10"/>
-      <c r="L47" s="8"/>
+    <row r="47" spans="5:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E47" s="24"/>
+      <c r="F47" s="24"/>
+      <c r="G47" s="24"/>
+      <c r="H47" s="24"/>
+      <c r="I47" s="24"/>
+      <c r="J47" s="24"/>
+      <c r="K47" s="24"/>
+      <c r="L47" s="28"/>
       <c r="M47" s="3"/>
       <c r="N47" s="3"/>
       <c r="O47" s="3"/>
@@ -2649,25 +2203,15 @@
       <c r="X47" s="3"/>
       <c r="Y47" s="3"/>
     </row>
-    <row r="48" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="B48" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C48" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="D48" s="10"/>
-      <c r="E48" s="10"/>
-      <c r="F48" s="10"/>
-      <c r="G48" s="10"/>
-      <c r="H48" s="10"/>
-      <c r="I48" s="10"/>
-      <c r="J48" s="10"/>
-      <c r="K48" s="10"/>
-      <c r="L48" s="8"/>
+    <row r="48" spans="5:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E48" s="24"/>
+      <c r="F48" s="24"/>
+      <c r="G48" s="24"/>
+      <c r="H48" s="24"/>
+      <c r="I48" s="24"/>
+      <c r="J48" s="24"/>
+      <c r="K48" s="24"/>
+      <c r="L48" s="28"/>
       <c r="M48" s="3"/>
       <c r="N48" s="3"/>
       <c r="O48" s="3"/>
@@ -2682,603 +2226,256 @@
       <c r="X48" s="3"/>
       <c r="Y48" s="3"/>
     </row>
-    <row r="49" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="B49" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C49" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="D49" s="10"/>
-      <c r="E49" s="10"/>
-      <c r="F49" s="10"/>
-      <c r="G49" s="10"/>
-      <c r="H49" s="10"/>
-      <c r="I49" s="10"/>
-      <c r="J49" s="10"/>
-      <c r="K49" s="10"/>
-      <c r="L49" s="8"/>
-      <c r="M49" s="3"/>
-      <c r="N49" s="3"/>
-      <c r="O49" s="3"/>
-      <c r="P49" s="3"/>
-      <c r="Q49" s="3"/>
-      <c r="R49" s="3"/>
-      <c r="S49" s="3"/>
-      <c r="T49" s="3"/>
-      <c r="U49" s="3"/>
-      <c r="V49" s="3"/>
-      <c r="W49" s="3"/>
-      <c r="X49" s="3"/>
-      <c r="Y49" s="3"/>
-    </row>
-    <row r="50" spans="1:25" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="B50" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C50" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="E50" s="10"/>
-      <c r="F50" s="10"/>
-      <c r="G50" s="10"/>
-      <c r="H50" s="10"/>
-      <c r="I50" s="10"/>
-      <c r="J50" s="10"/>
-      <c r="K50" s="10"/>
-      <c r="L50" s="8"/>
-      <c r="M50" s="3"/>
-      <c r="N50" s="3"/>
-      <c r="O50" s="3"/>
-      <c r="P50" s="3"/>
-      <c r="Q50" s="3"/>
-      <c r="R50" s="3"/>
-      <c r="S50" s="3"/>
-      <c r="T50" s="3"/>
-      <c r="U50" s="3"/>
-      <c r="V50" s="3"/>
-      <c r="W50" s="3"/>
-      <c r="X50" s="3"/>
-      <c r="Y50" s="3"/>
-    </row>
-    <row r="51" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B51" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C51" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="D51" s="10"/>
-      <c r="E51" s="10"/>
-      <c r="F51" s="10"/>
-      <c r="G51" s="10"/>
-      <c r="H51" s="10"/>
-      <c r="I51" s="10"/>
-      <c r="J51" s="10"/>
-      <c r="K51" s="10"/>
-      <c r="L51" s="8"/>
-    </row>
-    <row r="52" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="B52" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C52" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="D52" s="10"/>
-      <c r="E52" s="10"/>
-      <c r="F52" s="10"/>
-      <c r="G52" s="10"/>
-      <c r="H52" s="10"/>
-      <c r="I52" s="10"/>
-      <c r="J52" s="10"/>
-      <c r="K52" s="10"/>
-      <c r="L52" s="8"/>
-    </row>
-    <row r="53" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="B53" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C53" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="D53" s="10"/>
-      <c r="E53" s="10"/>
-      <c r="F53" s="10"/>
-      <c r="G53" s="10"/>
-      <c r="H53" s="10"/>
-      <c r="I53" s="10"/>
-      <c r="J53" s="10"/>
-      <c r="K53" s="10"/>
-      <c r="L53" s="8"/>
-    </row>
-    <row r="54" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="10" t="s">
-        <v>111</v>
-      </c>
-      <c r="B54" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C54" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="D54" s="10"/>
-      <c r="E54" s="10"/>
-      <c r="F54" s="10"/>
-      <c r="G54" s="10"/>
-      <c r="H54" s="10"/>
-      <c r="I54" s="10"/>
-      <c r="J54" s="10"/>
-      <c r="K54" s="10"/>
-      <c r="L54" s="8"/>
-    </row>
-    <row r="55" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="B55" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C55" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="D55" s="10"/>
-      <c r="E55" s="10"/>
-      <c r="F55" s="10"/>
-      <c r="G55" s="10"/>
-      <c r="H55" s="10"/>
-      <c r="I55" s="10"/>
-      <c r="J55" s="10"/>
-      <c r="K55" s="10"/>
-      <c r="L55" s="8"/>
-    </row>
-    <row r="56" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="10" t="s">
-        <v>115</v>
-      </c>
-      <c r="B56" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C56" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="D56" s="10"/>
-      <c r="E56" s="10"/>
-      <c r="F56" s="10"/>
-      <c r="G56" s="10"/>
-      <c r="H56" s="10"/>
-      <c r="I56" s="10"/>
-      <c r="J56" s="10"/>
-      <c r="K56" s="10"/>
-      <c r="L56" s="8"/>
-    </row>
-    <row r="57" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="B57" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C57" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="D57" s="10"/>
-      <c r="E57" s="10"/>
-      <c r="F57" s="10"/>
-      <c r="G57" s="10"/>
-      <c r="H57" s="10"/>
-      <c r="I57" s="10"/>
-      <c r="J57" s="10"/>
-      <c r="K57" s="10"/>
-      <c r="L57" s="8"/>
-    </row>
-    <row r="58" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="B58" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C58" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="D58" s="10"/>
-      <c r="E58" s="10"/>
-      <c r="F58" s="10"/>
-      <c r="G58" s="10"/>
-      <c r="H58" s="10"/>
-      <c r="I58" s="10"/>
-      <c r="J58" s="10"/>
-      <c r="K58" s="10"/>
-      <c r="L58" s="8"/>
-    </row>
-    <row r="59" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="B59" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C59" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="D59" s="10"/>
-      <c r="E59" s="10"/>
-      <c r="F59" s="10"/>
-      <c r="G59" s="10"/>
-      <c r="H59" s="10"/>
-      <c r="I59" s="10"/>
-      <c r="J59" s="10"/>
-      <c r="K59" s="10"/>
-      <c r="L59" s="8"/>
-    </row>
-    <row r="60" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="B60" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C60" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="D60" s="10"/>
-      <c r="E60" s="10"/>
-      <c r="F60" s="10"/>
-      <c r="G60" s="10"/>
-      <c r="H60" s="10"/>
-      <c r="I60" s="10"/>
-      <c r="J60" s="10"/>
-      <c r="K60" s="10"/>
-      <c r="L60" s="8"/>
-    </row>
-    <row r="61" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="10" t="s">
-        <v>125</v>
-      </c>
-      <c r="B61" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C61" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="D61" s="10"/>
-      <c r="E61" s="10"/>
-      <c r="F61" s="10"/>
-      <c r="G61" s="10"/>
-      <c r="H61" s="10"/>
-      <c r="I61" s="10"/>
-      <c r="J61" s="10"/>
-      <c r="K61" s="10"/>
-      <c r="L61" s="8"/>
-    </row>
-    <row r="62" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="B62" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C62" s="10" t="s">
-        <v>128</v>
-      </c>
-      <c r="D62" s="10"/>
-      <c r="E62" s="10"/>
-      <c r="F62" s="10"/>
-      <c r="G62" s="10"/>
-      <c r="H62" s="10"/>
-      <c r="I62" s="10"/>
-      <c r="J62" s="10"/>
-      <c r="K62" s="10"/>
-      <c r="L62" s="8"/>
-    </row>
-    <row r="63" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="B63" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="C63" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="D63" s="10"/>
-      <c r="E63" s="10"/>
-      <c r="F63" s="10"/>
-      <c r="G63" s="10"/>
-      <c r="H63" s="10"/>
-      <c r="I63" s="10"/>
-      <c r="J63" s="10"/>
-      <c r="K63" s="10"/>
-      <c r="L63" s="8"/>
-    </row>
-    <row r="64" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="B64" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C64" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="D64" s="10"/>
-      <c r="E64" s="10"/>
-      <c r="F64" s="10"/>
-      <c r="G64" s="10"/>
-      <c r="H64" s="10"/>
-      <c r="I64" s="10"/>
-      <c r="J64" s="10"/>
-      <c r="K64" s="10"/>
-      <c r="L64" s="8"/>
-    </row>
-    <row r="65" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="B65" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C65" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="D65" s="10"/>
-      <c r="E65" s="10"/>
-      <c r="F65" s="10"/>
-      <c r="G65" s="10"/>
-      <c r="H65" s="10"/>
-      <c r="I65" s="10"/>
-      <c r="J65" s="10"/>
-      <c r="K65" s="10"/>
-      <c r="L65" s="8"/>
-    </row>
-    <row r="66" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="B66" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C66" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="D66" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="E66" s="10"/>
-      <c r="F66" s="10"/>
-      <c r="G66" s="10"/>
-      <c r="H66" s="10"/>
-      <c r="I66" s="10"/>
-      <c r="J66" s="10"/>
-      <c r="K66" s="10"/>
-      <c r="L66" s="8"/>
-    </row>
-    <row r="67" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="10" t="s">
-        <v>137</v>
-      </c>
-      <c r="B67" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C67" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="D67" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="E67" s="10"/>
-      <c r="F67" s="10"/>
-      <c r="G67" s="10"/>
-      <c r="H67" s="10"/>
-      <c r="I67" s="10"/>
-      <c r="J67" s="10"/>
-      <c r="K67" s="10"/>
-      <c r="L67" s="8"/>
-    </row>
-    <row r="68" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="B68" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C68" s="10" t="s">
-        <v>140</v>
-      </c>
-      <c r="D68" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="E68" s="10"/>
-      <c r="F68" s="10"/>
-      <c r="G68" s="10"/>
-      <c r="H68" s="10"/>
-      <c r="I68" s="10"/>
-      <c r="J68" s="10"/>
-      <c r="K68" s="10"/>
-      <c r="L68" s="8"/>
-    </row>
-    <row r="69" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="B69" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C69" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="D69" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="E69" s="10"/>
-      <c r="F69" s="10"/>
-      <c r="G69" s="10"/>
-      <c r="H69" s="10"/>
-      <c r="I69" s="10"/>
-      <c r="J69" s="10"/>
-      <c r="K69" s="10"/>
-      <c r="L69" s="8"/>
-    </row>
-    <row r="70" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="B70" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C70" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="D70" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="E70" s="13"/>
-      <c r="F70" s="13"/>
-      <c r="G70" s="13"/>
-      <c r="H70" s="10"/>
-      <c r="I70" s="10"/>
-      <c r="J70" s="10"/>
-      <c r="K70" s="10"/>
-      <c r="L70" s="8"/>
-    </row>
-    <row r="71" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="B71" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C71" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="D71" s="10" t="s">
-        <v>156</v>
-      </c>
-      <c r="E71" s="13"/>
-      <c r="F71" s="13"/>
-      <c r="G71" s="13"/>
-      <c r="H71" s="13"/>
-      <c r="I71" s="10"/>
-      <c r="J71" s="10"/>
-      <c r="K71" s="10"/>
-      <c r="L71" s="8"/>
-    </row>
-    <row r="72" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="B72" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="C72" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="D72" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="E72" s="13"/>
-      <c r="F72" s="13"/>
-      <c r="G72" s="13"/>
-      <c r="H72" s="13"/>
-      <c r="I72" s="13"/>
-      <c r="J72" s="13"/>
-      <c r="K72" s="13"/>
-    </row>
-    <row r="73" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="B73" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="C73" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="D73" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="E73" s="13"/>
-      <c r="F73" s="13"/>
-      <c r="G73" s="13"/>
-      <c r="H73" s="13"/>
-      <c r="I73" s="13"/>
-      <c r="J73" s="13"/>
-      <c r="K73" s="13"/>
-    </row>
-    <row r="74" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="B74" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="C74" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="D74" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="E74" s="13"/>
-      <c r="F74" s="13"/>
-      <c r="G74" s="13"/>
-      <c r="H74" s="13"/>
-      <c r="I74" s="13"/>
-      <c r="J74" s="13"/>
-      <c r="K74" s="13"/>
-    </row>
-    <row r="75" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="B75" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="C75" s="13" t="s">
-        <v>152</v>
-      </c>
-      <c r="D75" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="H75" s="13"/>
-      <c r="I75" s="13"/>
-      <c r="J75" s="13"/>
-      <c r="K75" s="13"/>
-    </row>
-    <row r="76" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="13" t="s">
-        <v>153</v>
-      </c>
-      <c r="B76" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="C76" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="D76" s="13"/>
-      <c r="I76" s="13"/>
-      <c r="J76" s="13"/>
-      <c r="K76" s="13"/>
-    </row>
-    <row r="77" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="78" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="79" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="80" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="49" spans="5:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E49" s="24"/>
+      <c r="F49" s="24"/>
+      <c r="G49" s="24"/>
+      <c r="H49" s="24"/>
+      <c r="I49" s="24"/>
+      <c r="J49" s="24"/>
+      <c r="K49" s="24"/>
+      <c r="L49" s="28"/>
+    </row>
+    <row r="50" spans="5:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E50" s="24"/>
+      <c r="F50" s="24"/>
+      <c r="G50" s="24"/>
+      <c r="H50" s="24"/>
+      <c r="I50" s="24"/>
+      <c r="J50" s="24"/>
+      <c r="K50" s="24"/>
+      <c r="L50" s="28"/>
+    </row>
+    <row r="51" spans="5:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E51" s="24"/>
+      <c r="F51" s="24"/>
+      <c r="G51" s="24"/>
+      <c r="H51" s="24"/>
+      <c r="I51" s="24"/>
+      <c r="J51" s="24"/>
+      <c r="K51" s="24"/>
+      <c r="L51" s="28"/>
+    </row>
+    <row r="52" spans="5:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E52" s="24"/>
+      <c r="F52" s="24"/>
+      <c r="G52" s="24"/>
+      <c r="H52" s="24"/>
+      <c r="I52" s="24"/>
+      <c r="J52" s="24"/>
+      <c r="K52" s="24"/>
+      <c r="L52" s="28"/>
+    </row>
+    <row r="53" spans="5:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E53" s="24"/>
+      <c r="F53" s="24"/>
+      <c r="G53" s="24"/>
+      <c r="H53" s="24"/>
+      <c r="I53" s="24"/>
+      <c r="J53" s="24"/>
+      <c r="K53" s="24"/>
+      <c r="L53" s="28"/>
+    </row>
+    <row r="54" spans="5:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E54" s="24"/>
+      <c r="F54" s="24"/>
+      <c r="G54" s="24"/>
+      <c r="H54" s="24"/>
+      <c r="I54" s="24"/>
+      <c r="J54" s="24"/>
+      <c r="K54" s="24"/>
+      <c r="L54" s="28"/>
+    </row>
+    <row r="55" spans="5:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E55" s="24"/>
+      <c r="F55" s="24"/>
+      <c r="G55" s="24"/>
+      <c r="H55" s="24"/>
+      <c r="I55" s="24"/>
+      <c r="J55" s="24"/>
+      <c r="K55" s="24"/>
+      <c r="L55" s="28"/>
+    </row>
+    <row r="56" spans="5:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E56" s="24"/>
+      <c r="F56" s="24"/>
+      <c r="G56" s="24"/>
+      <c r="H56" s="24"/>
+      <c r="I56" s="24"/>
+      <c r="J56" s="24"/>
+      <c r="K56" s="24"/>
+      <c r="L56" s="28"/>
+    </row>
+    <row r="57" spans="5:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E57" s="24"/>
+      <c r="F57" s="24"/>
+      <c r="G57" s="24"/>
+      <c r="H57" s="24"/>
+      <c r="I57" s="24"/>
+      <c r="J57" s="24"/>
+      <c r="K57" s="24"/>
+      <c r="L57" s="28"/>
+    </row>
+    <row r="58" spans="5:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E58" s="24"/>
+      <c r="F58" s="24"/>
+      <c r="G58" s="24"/>
+      <c r="H58" s="24"/>
+      <c r="I58" s="24"/>
+      <c r="J58" s="24"/>
+      <c r="K58" s="24"/>
+      <c r="L58" s="28"/>
+    </row>
+    <row r="59" spans="5:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E59" s="24"/>
+      <c r="F59" s="24"/>
+      <c r="G59" s="24"/>
+      <c r="H59" s="24"/>
+      <c r="I59" s="24"/>
+      <c r="J59" s="24"/>
+      <c r="K59" s="24"/>
+      <c r="L59" s="28"/>
+    </row>
+    <row r="60" spans="5:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E60" s="24"/>
+      <c r="F60" s="24"/>
+      <c r="G60" s="24"/>
+      <c r="H60" s="24"/>
+      <c r="I60" s="24"/>
+      <c r="J60" s="24"/>
+      <c r="K60" s="24"/>
+      <c r="L60" s="28"/>
+    </row>
+    <row r="61" spans="5:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E61" s="24"/>
+      <c r="F61" s="24"/>
+      <c r="G61" s="24"/>
+      <c r="H61" s="24"/>
+      <c r="I61" s="24"/>
+      <c r="J61" s="24"/>
+      <c r="K61" s="24"/>
+      <c r="L61" s="28"/>
+    </row>
+    <row r="62" spans="5:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E62" s="24"/>
+      <c r="F62" s="24"/>
+      <c r="G62" s="24"/>
+      <c r="H62" s="24"/>
+      <c r="I62" s="24"/>
+      <c r="J62" s="24"/>
+      <c r="K62" s="24"/>
+      <c r="L62" s="28"/>
+    </row>
+    <row r="63" spans="5:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E63" s="24"/>
+      <c r="F63" s="24"/>
+      <c r="G63" s="24"/>
+      <c r="H63" s="24"/>
+      <c r="I63" s="24"/>
+      <c r="J63" s="24"/>
+      <c r="K63" s="24"/>
+      <c r="L63" s="28"/>
+    </row>
+    <row r="64" spans="5:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E64" s="24"/>
+      <c r="F64" s="24"/>
+      <c r="G64" s="24"/>
+      <c r="H64" s="24"/>
+      <c r="I64" s="24"/>
+      <c r="J64" s="24"/>
+      <c r="K64" s="24"/>
+      <c r="L64" s="28"/>
+    </row>
+    <row r="65" spans="5:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E65" s="24"/>
+      <c r="F65" s="24"/>
+      <c r="G65" s="24"/>
+      <c r="H65" s="24"/>
+      <c r="I65" s="24"/>
+      <c r="J65" s="24"/>
+      <c r="K65" s="24"/>
+      <c r="L65" s="28"/>
+    </row>
+    <row r="66" spans="5:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E66" s="24"/>
+      <c r="F66" s="24"/>
+      <c r="G66" s="24"/>
+      <c r="H66" s="24"/>
+      <c r="I66" s="24"/>
+      <c r="J66" s="24"/>
+      <c r="K66" s="24"/>
+      <c r="L66" s="28"/>
+    </row>
+    <row r="67" spans="5:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E67" s="24"/>
+      <c r="F67" s="24"/>
+      <c r="G67" s="24"/>
+      <c r="H67" s="24"/>
+      <c r="I67" s="24"/>
+      <c r="J67" s="24"/>
+      <c r="K67" s="24"/>
+      <c r="L67" s="28"/>
+    </row>
+    <row r="68" spans="5:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E68" s="24"/>
+      <c r="F68" s="24"/>
+      <c r="G68" s="24"/>
+      <c r="H68" s="24"/>
+      <c r="I68" s="24"/>
+      <c r="J68" s="24"/>
+      <c r="K68" s="24"/>
+      <c r="L68" s="28"/>
+    </row>
+    <row r="69" spans="5:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E69" s="12"/>
+      <c r="F69" s="12"/>
+      <c r="G69" s="12"/>
+      <c r="H69" s="12"/>
+      <c r="I69" s="24"/>
+      <c r="J69" s="24"/>
+      <c r="K69" s="24"/>
+      <c r="L69" s="28"/>
+    </row>
+    <row r="70" spans="5:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E70" s="12"/>
+      <c r="F70" s="12"/>
+      <c r="G70" s="12"/>
+      <c r="H70" s="12"/>
+      <c r="I70" s="12"/>
+      <c r="J70" s="12"/>
+      <c r="K70" s="12"/>
+    </row>
+    <row r="71" spans="5:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E71" s="12"/>
+      <c r="F71" s="12"/>
+      <c r="G71" s="12"/>
+      <c r="H71" s="12"/>
+      <c r="I71" s="12"/>
+      <c r="J71" s="12"/>
+      <c r="K71" s="12"/>
+    </row>
+    <row r="72" spans="5:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H72" s="12"/>
+      <c r="I72" s="12"/>
+      <c r="J72" s="12"/>
+      <c r="K72" s="12"/>
+    </row>
+    <row r="73" spans="5:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I73" s="12"/>
+      <c r="J73" s="12"/>
+      <c r="K73" s="12"/>
+    </row>
+    <row r="74" spans="5:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I74" s="12"/>
+      <c r="J74" s="12"/>
+      <c r="K74" s="12"/>
+    </row>
+    <row r="75" spans="5:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="76" spans="5:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="77" spans="5:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="78" spans="5:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="79" spans="5:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="80" spans="5:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -4185,8 +3382,6 @@
     <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="E2:H2"/>
@@ -4195,6 +3390,6 @@
     <mergeCell ref="I2:L2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.25" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup paperSize="9" scale="37" orientation="portrait"/>
+  <pageSetup paperSize="9" scale="38" orientation="landscape"/>
 </worksheet>
 </file>